--- a/output/sonuclar.xlsx
+++ b/output/sonuclar.xlsx
@@ -494,21 +494,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>'Dy-0' referansina gore hicbir numunede hicbir cizgide 3 sigma'yi asan fark yok: spektrumlar istatistiksel olarak ayirt edilemiyor. Numunenin isin yolunda oldugundan ve kalinligin yeterli oldugundan emin olun (numunesiz olcumle karsilastirinca netlesir).</t>
+          <t>'Dy-0' referansına göre hiçbir numunede hiçbir çizgide 3σ'yı aşan fark yok: spektrumlar istatistiksel olarak ayırt edilemiyor. Numunenin ışın yolunda olduğundan ve kalınlığın yeterli olduğundan emin olun (numunesiz ölçümle karşılaştırınca netleşir).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spektrumlarda tespit edilemeyen cizgiler (analiz disi birakildi): Am-241 59.5 (en yuksek 2.2 sigma); Co-57 122 (en yuksek 2.1 sigma)</t>
+          <t>Spektrumlarda tespit edilemeyen çizgiler (analiz dışı bırakıldı): Am-241 59.5 (en yüksek 2.2σ); Co-57 122 (en yüksek 2.1σ)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Numunesiz (I0) spektrum tanimli degil: LAC/MAC/HVL/TVL/MFP/RPE/Zeff/Neff hesaplanmadi.</t>
+          <t>Numunesiz (I0) spektrum tanımlı değil: LAC/MAC/HVL/TVL/MFP/RPE/Zeff/Neff hesaplanmadı.</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
@@ -4242,34 +4242,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.8091065333821519</v>
+        <v>0.8091066252691731</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>71.40601677255438</v>
+        <v>71.40602488185262</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.145752233243117</v>
+        <v>2.145752499648045</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>33.27784805081173</v>
+        <v>33.2778476984484</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>3.770736065641922e+23</v>
+        <v>3.770736025715389e+23</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5.151338566084147</v>
+        <v>5.151339151101245</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.1345567121376085</v>
+        <v>0.1345566968565379</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.446987722405593</v>
+        <v>0.4469876716429753</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.1941243013192515</v>
+        <v>0.1941242792733268</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>2.400714530912243e+24</v>
+        <v>2.400714505492217e+24</v>
       </c>
     </row>
     <row r="3">
@@ -4287,34 +4287,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1461871182359844</v>
+        <v>0.1461871446496136</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12.90144052236912</v>
+        <v>12.90144285344911</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4279947387244372</v>
+        <v>0.4279948024046465</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30.14392317255951</v>
+        <v>30.14392413404001</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>3.415628861973148e+23</v>
+        <v>3.415628970919171e+23</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.930729525673042</v>
+        <v>0.9307296938406953</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.7447353516143232</v>
+        <v>0.7447352170528097</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.473957287783439</v>
+        <v>2.473956840779767</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1.074425998548683</v>
+        <v>1.074425804417454</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>2.174628427552444e+24</v>
+        <v>2.174628496915108e+24</v>
       </c>
     </row>
     <row r="4">
@@ -4332,34 +4332,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.1212976334572946</v>
+        <v>0.1212976516304759</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10.70487073305073</v>
+        <v>10.7048723368871</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.3742958260370648</v>
+        <v>0.3742958680525469</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>28.60002700642107</v>
+        <v>28.60002808095189</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3.240688915544655e+23</v>
+        <v>3.240689037300489e+23</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.7722656429325577</v>
+        <v>0.7722657586357509</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.8975501977892316</v>
+        <v>0.8975500633155447</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.981597218607758</v>
+        <v>2.981596771895839</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1.294891219299433</v>
+        <v>1.294891025294911</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>2.063249411859816e+24</v>
+        <v>2.063249489378102e+24</v>
       </c>
     </row>
     <row r="5">
@@ -4377,34 +4377,34 @@
         <v>661.657</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.07923019671215378</v>
+        <v>0.07923020228576637</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.992296467650345</v>
+        <v>6.992296959537949</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.2669193487862835</v>
+        <v>0.2669193626578095</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.19628925158559</v>
+        <v>26.19628973302349</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.968319721759537e+23</v>
+        <v>2.9683197763116e+23</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.5044348934072695</v>
+        <v>0.5044349288927888</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.374106330904261</v>
+        <v>1.374106234239907</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4.564682425993457</v>
+        <v>4.564682104881422</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1.982416389249707</v>
+        <v>1.982416249792522</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.889840117252644e+24</v>
+        <v>1.889840151984306e+24</v>
       </c>
     </row>
     <row r="6">
@@ -4422,34 +4422,34 @@
         <v>1173.228</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.05729122902391755</v>
+        <v>0.05729123209776895</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.056118436593945</v>
+        <v>5.056118707870315</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.1984537421446335</v>
+        <v>0.1984537492477799</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>25.47756662058322</v>
+        <v>25.47756707562872</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>2.886880761470529e+23</v>
+        <v>2.88688081303205e+23</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.3647560678265759</v>
+        <v>0.3647560873968656</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.900303358049971</v>
+        <v>1.900303256092832</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6.312671113914998</v>
+        <v>6.312670775220713</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2.741558230843338</v>
+        <v>2.741558083750279</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.837990374405442e+24</v>
+        <v>1.837990407233116e+24</v>
       </c>
     </row>
     <row r="7">
@@ -4467,34 +4467,34 @@
         <v>1332.492</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.05355073783901342</v>
+        <v>0.05355074364974851</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.72600915522357</v>
+        <v>4.726009668037928</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1859305175663731</v>
+        <v>0.1859305318902437</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.41814661241121</v>
+        <v>25.41814741232349</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.880147839092471e+23</v>
+        <v>2.880147929731086e+23</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.3409414825996467</v>
+        <v>0.3409415195948539</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.033038559211872</v>
+        <v>2.033038338608987</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>6.753607907835242</v>
+        <v>6.753607175008323</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2.933054647311011</v>
+        <v>2.933054329048324</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.833703724715004e+24</v>
+        <v>1.833703782421891e+24</v>
       </c>
     </row>
     <row r="8">
@@ -4512,34 +4512,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.029800480263824</v>
+        <v>1.029800575431292</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>91.79159321512098</v>
+        <v>91.7916016979035</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.410539756946668</v>
+        <v>2.410540022146601</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>38.07926957047564</v>
+        <v>38.07926890015397</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>4.27207424103318e+23</v>
+        <v>4.272074165830478e+23</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6.501267738636222</v>
+        <v>6.501268339441137</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1066172335036532</v>
+        <v>0.1066172236507822</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.3541747833749517</v>
+        <v>0.3541747506444229</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.1538161540490211</v>
+        <v>0.153816139834333</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2.697017429354127e+24</v>
+        <v>2.697017381877658e+24</v>
       </c>
     </row>
     <row r="9">
@@ -4557,34 +4557,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.1525428502488606</v>
+        <v>0.1525428794200443</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13.59695545522695</v>
+        <v>13.59695805540968</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.4368719043062879</v>
+        <v>0.4368719703422631</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>31.12343760539523</v>
+        <v>31.12343885270844</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>3.491706579096327e+23</v>
+        <v>3.491706719031118e+23</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.963023352667757</v>
+        <v>0.9630235368293291</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.7197615495406174</v>
+        <v>0.7197614118986873</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2.39099611303864</v>
+        <v>2.390995655802044</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1.038396418144805</v>
+        <v>1.038396219569475</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.204360919471232e+24</v>
+        <v>2.204361007813931e+24</v>
       </c>
     </row>
     <row r="10">
@@ -4602,34 +4602,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.1249338868697428</v>
+        <v>0.1249339071389403</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.13602172664887</v>
+        <v>11.13602353335022</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.3796620005750761</v>
+        <v>0.3796620446329574</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>29.33140980604083</v>
+        <v>29.33141116098688</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3.290660816212969e+23</v>
+        <v>3.290660968222978e+23</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.7887242856602692</v>
+        <v>0.7887244136224152</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8788206387986229</v>
+        <v>0.8788204962193228</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2.919378970392005</v>
+        <v>2.919378496753822</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.267870177425644</v>
+        <v>1.267869971727195</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>2.077438048752797e+24</v>
+        <v>2.077438144718742e+24</v>
       </c>
     </row>
     <row r="11">
@@ -4647,34 +4647,34 @@
         <v>661.657</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.07975900966766181</v>
+        <v>0.07975901566146988</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7.109344684690087</v>
+        <v>7.109345218950074</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.2681722698602301</v>
+        <v>0.2681722842926609</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>26.51036473083305</v>
+        <v>26.5103652963314</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.97417065937622e+23</v>
+        <v>2.974170722818901e+23</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.5035292625665713</v>
+        <v>0.5035293004062809</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.376577752456452</v>
+        <v>1.376577649008048</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4.572892310681989</v>
+        <v>4.57289196703383</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1.985981896866998</v>
+        <v>1.985981747622499</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.877633592872999e+24</v>
+        <v>1.877633632925209e+24</v>
       </c>
     </row>
     <row r="12">
@@ -4692,34 +4692,34 @@
         <v>1173.228</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.05724513123965686</v>
+        <v>0.05724513462334656</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.102562973121375</v>
+        <v>5.102563274727633</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.1988364989844983</v>
+        <v>0.1988365064139896</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>25.66210428759954</v>
+        <v>25.66210484559504</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.879005189289709e+23</v>
+        <v>2.879005251890653e+23</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.3613961462001191</v>
+        <v>0.3613961675618033</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.917970592237923</v>
+        <v>1.917970478869033</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>6.37136039552291</v>
+        <v>6.371360018919611</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2.76704666199252</v>
+        <v>2.767046498435785</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>1.81755436273445e+24</v>
+        <v>1.817554402255261e+24</v>
       </c>
     </row>
     <row r="13">
@@ -4737,34 +4737,34 @@
         <v>1332.492</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.05347405147216455</v>
+        <v>0.05347405777635045</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.766426579097994</v>
+        <v>4.766427141023609</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1862405724407968</v>
+        <v>0.1862405873506288</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>25.59284755534766</v>
+        <v>25.59284852366803</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.871235347451651e+23</v>
+        <v>2.871235456086522e+23</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.3375888168173044</v>
+        <v>0.3375888566164705</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.053229094182528</v>
+        <v>2.053228852122388</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>6.82067941320507</v>
+        <v>6.820678609098692</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2.962183431986071</v>
+        <v>2.962183082767108</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1.812649157984193e+24</v>
+        <v>1.812649226566836e+24</v>
       </c>
     </row>
     <row r="14">
@@ -4782,34 +4782,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.249792779145695</v>
+        <v>1.249792877549543</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>112.4716437442313</v>
+        <v>112.4716525998134</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2.67834693064591</v>
+        <v>2.678347194417567</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>41.99293319969852</v>
+        <v>41.99293237046941</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>4.666284135357681e+23</v>
+        <v>4.666284043213161e+23</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7.842699647695064</v>
+        <v>7.842700265198891</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.08838119674309576</v>
+        <v>0.08838118978430283</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.2935959805206573</v>
+        <v>0.2935959574040475</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.1275071142490961</v>
+        <v>0.12750710420968</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>2.928186620619652e+24</v>
+        <v>2.928186562797122e+24</v>
       </c>
     </row>
     <row r="15">
@@ -4827,34 +4827,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.1588849990242324</v>
+        <v>0.1588850309393838</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14.29841594921937</v>
+        <v>14.29841882133513</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.445855994381512</v>
+        <v>0.4458560627627444</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>32.06958329461068</v>
+        <v>32.06958481787836</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3.563594546814078e+23</v>
+        <v>3.563594716080649e+23</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.9970351458768633</v>
+        <v>0.9970353461508212</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6952083719680139</v>
+        <v>0.6952082323218791</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2.309432222641449</v>
+        <v>2.309431758747031</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1.002973670622743</v>
+        <v>1.002973469155957</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>2.23622685001677e+24</v>
+        <v>2.236226956234929e+24</v>
       </c>
     </row>
     <row r="16">
@@ -4872,34 +4872,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.1285623856593195</v>
+        <v>0.1285624080162978</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>11.56961624363636</v>
+        <v>11.56961825559076</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.3850927338388263</v>
+        <v>0.3850927799458223</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30.04371473931423</v>
+        <v>30.04371636678949</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.338478614689392e+23</v>
+        <v>3.338478795535582e+23</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.8067546824893619</v>
+        <v>0.8067548227838718</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.8591796187920921</v>
+        <v>0.8591794693809203</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2.854132914220065</v>
+        <v>2.854132417886896</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.239534175264221</v>
+        <v>1.239533959709465</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.094962100289887e+24</v>
+        <v>2.094962213774488e+24</v>
       </c>
     </row>
     <row r="17">
@@ -4917,34 +4917,34 @@
         <v>661.657</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.08028668259639675</v>
+        <v>0.08028668900873268</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7.225177895939369</v>
+        <v>7.225178472999803</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.2694403817019703</v>
+        <v>0.2694403966973864</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>26.81549755200089</v>
+        <v>26.81549820131291</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.979756860840643e+23</v>
+        <v>2.979756932992649e+23</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.5038149906289088</v>
+        <v>0.5038150308675992</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.375797055372835</v>
+        <v>1.375796945490699</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4.570298891106326</v>
+        <v>4.570298526085772</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1.984855589056028</v>
+        <v>1.984855430529615</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1.86985702531472e+24</v>
+        <v>1.869857070591547e+24</v>
       </c>
     </row>
     <row r="18">
@@ -4962,34 +4962,34 @@
         <v>1173.228</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.05719907458110665</v>
+        <v>0.05719907827434033</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>5.147472481944931</v>
+        <v>5.147472814307279</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.1992238473005391</v>
+        <v>0.1992238550627248</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>25.83763214942693</v>
+        <v>25.83763281102365</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2.871095772727398e+23</v>
+        <v>2.871095846244489e+23</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.3589356328113604</v>
+        <v>0.3589356559871404</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.93111833208332</v>
+        <v>1.93111820739475</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>6.415036241899604</v>
+        <v>6.415035827693142</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2.786014841066372</v>
+        <v>2.786014661178791</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.801670019301897e+24</v>
+        <v>1.801670065435342e+24</v>
       </c>
     </row>
     <row r="19">
@@ -5007,34 +5007,34 @@
         <v>1332.492</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.0533974356728467</v>
+        <v>0.0533974424692118</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4.805354505214184</v>
+        <v>4.80535511683426</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.1865541480816297</v>
+        <v>0.1865541635834549</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>25.75849722254113</v>
+        <v>25.75849836063609</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>2.862302244251456e+23</v>
+        <v>2.862302370717365e+23</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.3350795883342475</v>
+        <v>0.3350796309827979</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.068604608253605</v>
+        <v>2.068604344963988</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>6.871755765371118</v>
+        <v>6.871754890741941</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2.984365609887533</v>
+        <v>2.984365230040908</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>1.796151904312674e+24</v>
+        <v>1.796151983672561e+24</v>
       </c>
     </row>
     <row r="20">
@@ -5052,34 +5052,34 @@
         <v>80.89906428571429</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1.68848209773271</v>
+        <v>1.688482202627127</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>155.0068093412279</v>
+        <v>155.0068189707935</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3.23011641645961</v>
+        <v>3.230116677541063</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>47.98799465906685</v>
+        <v>47.9879937615111</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5.227310350576718e+23</v>
+        <v>5.22731025280638e+23</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10.60507464217619</v>
+        <v>10.60507530100055</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.06535995303638045</v>
+        <v>0.06535994897599165</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.2171210642720708</v>
+        <v>0.2171210507837512</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.09429448011832162</v>
+        <v>0.09429447426041884</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>3.283186509358061e+24</v>
+        <v>3.28318644795014e+24</v>
       </c>
     </row>
     <row r="21">
@@ -5097,34 +5097,34 @@
         <v>295.4176231113203</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.1715250654019454</v>
+        <v>0.171525102794321</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>15.74642286447853</v>
+        <v>15.74642629719057</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.4643614729925126</v>
+        <v>0.4643615462518457</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>33.90983916689493</v>
+        <v>33.90984120948404</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>3.693783299819775e+23</v>
+        <v>3.693783522318075e+23</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1.077320348278719</v>
+        <v>1.077320583133998</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6433993209795177</v>
+        <v>0.643399180718829</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.137326280593312</v>
+        <v>2.13732581465739</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.9282290096884765</v>
+        <v>0.9282288073350766</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>2.320003727561804e+24</v>
+        <v>2.320003867309277e+24</v>
       </c>
     </row>
     <row r="22">
@@ -5142,34 +5142,34 @@
         <v>359.5183270178899</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.1357940088838202</v>
+        <v>0.1357940354059685</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>12.46622399668903</v>
+        <v>12.46622643148747</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.396279117469294</v>
+        <v>0.3962791678195</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>31.45819057108147</v>
+        <v>31.45819271823463</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>3.426726337512406e+23</v>
+        <v>3.42672657140082e+23</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.852899537464461</v>
+        <v>0.8528997040456542</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8126949894011728</v>
+        <v>0.8126948306724261</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2.699714317865943</v>
+        <v>2.69971379058046</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1.172471030964381</v>
+        <v>1.172470801967205</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>2.152269700485917e+24</v>
+        <v>2.152269847387332e+24</v>
       </c>
     </row>
     <row r="23">
@@ -5187,34 +5187,34 @@
         <v>661.657</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.08133826306585649</v>
+        <v>0.08133827031309329</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7.467052598381609</v>
+        <v>7.467053263695772</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.2720523796495957</v>
+        <v>0.2720523958091977</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>27.44711370655606</v>
+        <v>27.44711452176567</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.989801565809512e+23</v>
+        <v>2.989801654609924e+23</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.510872073939467</v>
+        <v>0.5108721194581535</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.356792073629916</v>
+        <v>1.356791952739794</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>4.507165708311702</v>
+        <v>4.507165306723408</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1.957437196143333</v>
+        <v>1.957437021735754</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.877844533458858e+24</v>
+        <v>1.877844589232917e+24</v>
       </c>
     </row>
     <row r="24">
@@ -5232,34 +5232,34 @@
         <v>1173.228</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.05710725653463142</v>
+        <v>0.05710726084448348</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5.242586603405906</v>
+        <v>5.242586999060926</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.2000217409107372</v>
+        <v>0.2000217493564276</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>26.21008386156128</v>
+        <v>26.21008473293036</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2.855052469527121e+23</v>
+        <v>2.855052564444956e+23</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.3586811604179309</v>
+        <v>0.3586811874873934</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.932488396525479</v>
+        <v>1.932488250681693</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>6.419587497461818</v>
+        <v>6.41958701297925</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2.787991426242773</v>
+        <v>2.787991215834667</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>1.793210871902159e+24</v>
+        <v>1.79321093151847e+24</v>
       </c>
     </row>
     <row r="25">
@@ -5277,34 +5277,34 @@
         <v>1332.492</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.05324475654119191</v>
+        <v>0.0532447643187437</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>4.887999604309189</v>
+        <v>4.888000318307571</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.1872003261754824</v>
+        <v>0.1872003428981714</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>26.11106350171183</v>
+        <v>26.11106498328598</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2.844266226933817e+23</v>
+        <v>2.844266388321013e+23</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.3344214417091362</v>
+        <v>0.3344214905586427</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.072675654460014</v>
+        <v>2.072675351700814</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>6.885279488139771</v>
+        <v>6.88527848239548</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2.990238888060749</v>
+        <v>2.990238451271553</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>1.786436212700015e+24</v>
+        <v>1.786436314064623e+24</v>
       </c>
     </row>
   </sheetData>
@@ -5385,13 +5385,13 @@
         <v>80.89906428571429</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.352557616883219</v>
+        <v>2.35255765896867</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>26.70152895162454</v>
+        <v>26.70152942929441</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.02595908203667767</v>
+        <v>0.02595908157228962</v>
       </c>
     </row>
     <row r="3">
@@ -5412,13 +5412,13 @@
         <v>295.4176231113203</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.4163622880996919</v>
+        <v>0.4163623946355609</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.725711969931503</v>
+        <v>4.725713179113615</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1466757146796639</v>
+        <v>0.1466756771493179</v>
       </c>
     </row>
     <row r="4">
@@ -5439,13 +5439,13 @@
         <v>359.5183270178899</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2821304751238382</v>
+        <v>0.2821305555687182</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.202180892655563</v>
+        <v>3.202181805704951</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2164609695066663</v>
+        <v>0.2164609077863869</v>
       </c>
     </row>
     <row r="5">
@@ -5466,13 +5466,13 @@
         <v>661.657</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1102033533310854</v>
+        <v>0.1102033739037272</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.250808060307819</v>
+        <v>1.250808293807304</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.554159509005214</v>
+        <v>0.5541594055553406</v>
       </c>
     </row>
     <row r="6">
@@ -5493,13 +5493,13 @@
         <v>1173.228</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.06166367792142712</v>
+        <v>0.06166369276333716</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.6998827444081978</v>
+        <v>0.6998829128638767</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.9903761538599614</v>
+        <v>0.9903759154851071</v>
       </c>
     </row>
     <row r="7">
@@ -5520,13 +5520,13 @@
         <v>1332.492</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.05610115372288973</v>
+        <v>0.05610117871916188</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6367480947547984</v>
+        <v>0.6367483784624873</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.088573623179611</v>
+        <v>1.088573138158028</v>
       </c>
     </row>
     <row r="8">
@@ -5547,13 +5547,13 @@
         <v>80.89906428571429</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1996495265144275</v>
+        <v>0.1996495455767022</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.4591939109831832</v>
+        <v>0.459193954826415</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.509486872497597</v>
+        <v>1.509486728373786</v>
       </c>
     </row>
     <row r="9">
@@ -5574,13 +5574,13 @@
         <v>295.4176231113203</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1103931810472376</v>
+        <v>0.1103931815987268</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.2539043164086464</v>
+        <v>0.2539043176770715</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2.729954300754617</v>
+        <v>2.729954287116635</v>
       </c>
     </row>
     <row r="10">
@@ -5601,13 +5601,13 @@
         <v>359.5183270178899</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.1020581609644876</v>
+        <v>0.1020581627180894</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.2347337702183215</v>
+        <v>0.2347337742516055</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2.952907798120663</v>
+        <v>2.952907747382689</v>
       </c>
     </row>
     <row r="11">
@@ -5628,13 +5628,13 @@
         <v>661.657</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.07883704400614537</v>
+        <v>0.07883704636894012</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.1813252012141343</v>
+        <v>0.1813252066485623</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3.822674266559227</v>
+        <v>3.822674151991329</v>
       </c>
     </row>
     <row r="12">
@@ -5655,13 +5655,13 @@
         <v>1173.228</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.05993790771013759</v>
+        <v>0.059937908254028</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.1378571877333165</v>
+        <v>0.1378571889842644</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5.028008999435216</v>
+        <v>5.028008953809903</v>
       </c>
     </row>
     <row r="13">
@@ -5682,13 +5682,13 @@
         <v>1332.492</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.05619604576989413</v>
+        <v>0.05619604768884361</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1292509052707565</v>
+        <v>0.1292509096843403</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5.36280329416596</v>
+        <v>5.362803111040117</v>
       </c>
     </row>
   </sheetData>
